--- a/data/final/input/ElectricityManagement.xlsx
+++ b/data/final/input/ElectricityManagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\as\Development\back_end_projects\java\DaElectric\data\final\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F50D7E5-1434-4614-8929-9B90C9EAD299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025A189A-9846-4935-8A1C-A840B5243C55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="11512" xr2:uid="{1CF578A3-021B-4651-B9BD-E4E2F9F1E764}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{1CF578A3-021B-4651-B9BD-E4E2F9F1E764}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="78">
   <si>
     <t>STT</t>
   </si>
@@ -77,9 +77,6 @@
     <t>PHổ H' Neng</t>
   </si>
   <si>
-    <t>Phận</t>
-  </si>
-  <si>
     <t>Trần Công Viên</t>
   </si>
   <si>
@@ -185,12 +182,6 @@
     <t>Trần Hữu Công</t>
   </si>
   <si>
-    <t>Lâm Văn Bộ</t>
-  </si>
-  <si>
-    <t>Sáu Lực</t>
-  </si>
-  <si>
     <t>Phan Đình Sỹ</t>
   </si>
   <si>
@@ -227,9 +218,6 @@
     <t>Trần Văn Cương(vĩnh)</t>
   </si>
   <si>
-    <t>Phan Đình Sỹ 2</t>
-  </si>
-  <si>
     <t>Lâm Văn Bộ 2</t>
   </si>
   <si>
@@ -242,19 +230,46 @@
     <t>chú Toàn</t>
   </si>
   <si>
-    <t>Nguyễn Văn Phú</t>
-  </si>
-  <si>
-    <t>Minh (nhà)</t>
-  </si>
-  <si>
-    <t>Đức rèn</t>
-  </si>
-  <si>
     <t>Vĩnh 2</t>
   </si>
   <si>
     <t>Thái Ninh Đậu 2</t>
+  </si>
+  <si>
+    <t>Khang nhà</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn Thìn</t>
+  </si>
+  <si>
+    <t>Trần Thị Viếng</t>
+  </si>
+  <si>
+    <t>Minh  ( nhà)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Đức rèn</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn PHú</t>
+  </si>
+  <si>
+    <t>An</t>
+  </si>
+  <si>
+    <t>phận</t>
+  </si>
+  <si>
+    <t>Sang 2</t>
+  </si>
+  <si>
+    <t>Sáu Lực 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sáu Lực </t>
+  </si>
+  <si>
+    <t>Thái Ngọc Hoà</t>
   </si>
 </sst>
 </file>
@@ -295,7 +310,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -318,12 +333,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -336,6 +360,10 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -651,14 +679,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F81E9876-7744-4322-9AD5-05539167F3DA}">
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="3.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.53125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.33203125" customWidth="1"/>
-    <col min="8" max="8" width="7.265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.796875" customWidth="1"/>
+    <col min="5" max="5" width="15.796875" customWidth="1"/>
+    <col min="7" max="7" width="9.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="23.25" x14ac:dyDescent="0.45">
@@ -698,28 +729,28 @@
         <v>9</v>
       </c>
       <c r="C2" s="3">
-        <v>36477</v>
+        <v>37504</v>
       </c>
       <c r="D2" s="3">
-        <v>36642</v>
+        <v>37504</v>
       </c>
       <c r="E2" s="4">
         <f>D2-C2</f>
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="F2" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G2" s="7">
         <f>E2*F2</f>
-        <v>634590</v>
+        <v>0</v>
       </c>
       <c r="H2" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I2" s="5">
         <f>G2+H2</f>
-        <v>654590</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
@@ -730,28 +761,28 @@
         <v>10</v>
       </c>
       <c r="C3" s="3">
-        <v>10736</v>
+        <v>14139</v>
       </c>
       <c r="D3" s="3">
-        <v>11031</v>
+        <v>14239</v>
       </c>
       <c r="E3" s="4">
         <f t="shared" ref="E3:E66" si="0">D3-C3</f>
-        <v>295</v>
+        <v>100</v>
       </c>
       <c r="F3" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G3" s="7">
         <f t="shared" ref="G3:G66" si="1">E3*F3</f>
-        <v>1134570</v>
+        <v>297100</v>
       </c>
       <c r="H3" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" ref="I3:I66" si="2">G3+H3</f>
-        <v>1154570</v>
+        <v>322100</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
@@ -762,28 +793,28 @@
         <v>11</v>
       </c>
       <c r="C4" s="3">
-        <v>1339</v>
+        <v>1637</v>
       </c>
       <c r="D4" s="3">
-        <v>1395</v>
+        <v>1637</v>
       </c>
       <c r="E4" s="4">
         <f t="shared" si="0"/>
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="F4" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G4" s="7">
         <f t="shared" si="1"/>
-        <v>215376</v>
+        <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I4" s="5">
         <f t="shared" si="2"/>
-        <v>235376</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
@@ -791,31 +822,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="C5" s="3">
-        <v>26800</v>
+        <v>688</v>
       </c>
       <c r="D5" s="3">
-        <v>26905</v>
+        <v>688</v>
       </c>
       <c r="E5" s="4">
         <f t="shared" si="0"/>
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="F5" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G5" s="7">
         <f t="shared" si="1"/>
-        <v>403830</v>
+        <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="2"/>
-        <v>423830</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
@@ -823,31 +854,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3">
-        <v>2237</v>
+        <v>30408</v>
       </c>
       <c r="D6" s="3">
-        <v>2904</v>
+        <v>30428</v>
       </c>
       <c r="E6" s="4">
         <f t="shared" si="0"/>
-        <v>667</v>
+        <v>20</v>
       </c>
       <c r="F6" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G6" s="7">
         <f t="shared" si="1"/>
-        <v>2565282</v>
+        <v>59420</v>
       </c>
       <c r="H6" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="2"/>
-        <v>2585282</v>
+        <v>84420</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
@@ -855,31 +886,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="C7" s="3">
-        <v>12340</v>
+        <v>11333</v>
       </c>
       <c r="D7" s="3">
-        <v>13742</v>
+        <v>11826</v>
       </c>
       <c r="E7" s="4">
         <f t="shared" si="0"/>
-        <v>1402</v>
+        <v>493</v>
       </c>
       <c r="F7" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G7" s="7">
         <f t="shared" si="1"/>
-        <v>5392092</v>
+        <v>1464703</v>
       </c>
       <c r="H7" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="2"/>
-        <v>5412092</v>
+        <v>1489703</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
@@ -887,31 +918,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3">
-        <v>42217</v>
+        <v>18310</v>
       </c>
       <c r="D8" s="3">
-        <v>42679</v>
+        <v>18375</v>
       </c>
       <c r="E8" s="4">
         <f t="shared" si="0"/>
-        <v>462</v>
+        <v>65</v>
       </c>
       <c r="F8" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G8" s="7">
         <f t="shared" si="1"/>
-        <v>1776852</v>
+        <v>193115</v>
       </c>
       <c r="H8" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="2"/>
-        <v>1796852</v>
+        <v>218115</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
@@ -919,31 +950,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3">
-        <v>424</v>
+        <v>45017</v>
       </c>
       <c r="D9" s="3">
-        <v>662</v>
+        <v>45017</v>
       </c>
       <c r="E9" s="4">
         <f t="shared" si="0"/>
-        <v>238</v>
+        <v>0</v>
       </c>
       <c r="F9" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G9" s="7">
         <f t="shared" si="1"/>
-        <v>915348</v>
+        <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="2"/>
-        <v>935348</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
@@ -951,31 +982,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C10" s="3">
-        <v>14427</v>
+        <v>1469</v>
       </c>
       <c r="D10" s="3">
-        <v>14537</v>
+        <v>1521</v>
       </c>
       <c r="E10" s="4">
         <f t="shared" si="0"/>
-        <v>110</v>
+        <v>52</v>
       </c>
       <c r="F10" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G10" s="7">
         <f t="shared" si="1"/>
-        <v>423060</v>
+        <v>154492</v>
       </c>
       <c r="H10" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" si="2"/>
-        <v>443060</v>
+        <v>179492</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
@@ -983,31 +1014,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="C11" s="3">
-        <v>29956</v>
+        <v>759</v>
       </c>
       <c r="D11" s="3">
-        <v>30103</v>
+        <v>874</v>
       </c>
       <c r="E11" s="4">
         <f t="shared" si="0"/>
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="F11" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G11" s="7">
         <f t="shared" si="1"/>
-        <v>565362</v>
+        <v>341665</v>
       </c>
       <c r="H11" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" si="2"/>
-        <v>585362</v>
+        <v>366665</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
@@ -1015,31 +1046,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C12" s="3">
-        <v>2452</v>
+        <v>16953</v>
       </c>
       <c r="D12" s="3">
-        <v>2519</v>
+        <v>17103</v>
       </c>
       <c r="E12" s="4">
         <f t="shared" si="0"/>
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="F12" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G12" s="7">
         <f t="shared" si="1"/>
-        <v>257682</v>
+        <v>445650</v>
       </c>
       <c r="H12" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="2"/>
-        <v>277682</v>
+        <v>470650</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
@@ -1047,31 +1078,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C13" s="3">
-        <v>7673</v>
+        <v>31728</v>
       </c>
       <c r="D13" s="3">
-        <v>8403</v>
+        <v>31829</v>
       </c>
       <c r="E13" s="4">
         <f t="shared" si="0"/>
-        <v>730</v>
+        <v>101</v>
       </c>
       <c r="F13" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G13" s="7">
         <f t="shared" si="1"/>
-        <v>2807580</v>
+        <v>300071</v>
       </c>
       <c r="H13" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="2"/>
-        <v>2827580</v>
+        <v>325071</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
@@ -1079,31 +1110,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C14" s="3">
-        <v>7627</v>
+        <v>3765</v>
       </c>
       <c r="D14" s="3">
-        <v>7627</v>
+        <v>3780</v>
       </c>
       <c r="E14" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F14" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G14" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>44565</v>
       </c>
       <c r="H14" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="2"/>
-        <v>20000</v>
+        <v>69565</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
@@ -1111,31 +1142,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C15" s="3">
-        <v>11089</v>
+        <v>11976</v>
       </c>
       <c r="D15" s="3">
-        <v>11181</v>
+        <v>11990</v>
       </c>
       <c r="E15" s="4">
         <f t="shared" si="0"/>
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="F15" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G15" s="7">
         <f t="shared" si="1"/>
-        <v>353832</v>
+        <v>41594</v>
       </c>
       <c r="H15" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="2"/>
-        <v>373832</v>
+        <v>66594</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
@@ -1143,31 +1174,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C16" s="3">
-        <v>1925</v>
+        <v>7628</v>
       </c>
       <c r="D16" s="3">
-        <v>2029</v>
+        <v>7628</v>
       </c>
       <c r="E16" s="4">
         <f t="shared" si="0"/>
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="F16" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G16" s="7">
         <f t="shared" si="1"/>
-        <v>399984</v>
+        <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" si="2"/>
-        <v>419984</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.45">
@@ -1175,31 +1206,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C17" s="3">
-        <v>8042</v>
+        <v>11484</v>
       </c>
       <c r="D17" s="3">
-        <v>8093</v>
+        <v>11484</v>
       </c>
       <c r="E17" s="4">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="F17" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G17" s="7">
         <f t="shared" si="1"/>
-        <v>196146</v>
+        <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="2"/>
-        <v>216146</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.45">
@@ -1207,31 +1238,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C18" s="3">
-        <v>7647</v>
+        <v>2528</v>
       </c>
       <c r="D18" s="3">
-        <v>7824</v>
+        <v>2528</v>
       </c>
       <c r="E18" s="4">
         <f t="shared" si="0"/>
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="F18" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G18" s="7">
         <f t="shared" si="1"/>
-        <v>680742</v>
+        <v>0</v>
       </c>
       <c r="H18" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="2"/>
-        <v>700742</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
@@ -1239,31 +1270,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C19" s="3">
-        <v>7055</v>
+        <v>8599</v>
       </c>
       <c r="D19" s="3">
-        <v>7067</v>
+        <v>8646</v>
       </c>
       <c r="E19" s="4">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="F19" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G19" s="7">
         <f t="shared" si="1"/>
-        <v>46152</v>
+        <v>139637</v>
       </c>
       <c r="H19" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="2"/>
-        <v>66152</v>
+        <v>164637</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.45">
@@ -1271,31 +1302,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C20" s="3">
-        <v>138051</v>
+        <v>9888</v>
       </c>
       <c r="D20" s="3">
-        <v>138717</v>
+        <v>9897</v>
       </c>
       <c r="E20" s="4">
         <f t="shared" si="0"/>
-        <v>666</v>
+        <v>9</v>
       </c>
       <c r="F20" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G20" s="7">
         <f t="shared" si="1"/>
-        <v>2561436</v>
+        <v>26739</v>
       </c>
       <c r="H20" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="2"/>
-        <v>2581436</v>
+        <v>51739</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.45">
@@ -1303,31 +1334,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C21" s="3">
-        <v>19371</v>
+        <v>7278</v>
       </c>
       <c r="D21" s="3">
-        <v>19873</v>
+        <v>7282</v>
       </c>
       <c r="E21" s="4">
         <f t="shared" si="0"/>
-        <v>502</v>
+        <v>4</v>
       </c>
       <c r="F21" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G21" s="7">
         <f t="shared" si="1"/>
-        <v>1930692</v>
+        <v>11884</v>
       </c>
       <c r="H21" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="2"/>
-        <v>1950692</v>
+        <v>36884</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.45">
@@ -1335,31 +1366,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C22" s="3">
-        <v>16667</v>
+        <v>149849</v>
       </c>
       <c r="D22" s="3">
-        <v>16667</v>
+        <v>149933</v>
       </c>
       <c r="E22" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F22" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G22" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>249564</v>
       </c>
       <c r="H22" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="2"/>
-        <v>20000</v>
+        <v>274564</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.45">
@@ -1367,64 +1398,63 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C23" s="3">
-        <v>11320</v>
+        <v>26126</v>
       </c>
       <c r="D23" s="3">
-        <v>11320</v>
+        <v>26146</v>
       </c>
       <c r="E23" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F23" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G23" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>59420</v>
       </c>
       <c r="H23" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="2"/>
-        <v>20000</v>
+        <v>84420</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" s="4">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="str">
-        <f>B64</f>
-        <v>Hùng Tuấn</v>
+      <c r="B24" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="C24" s="3">
-        <v>2090</v>
+        <v>17576</v>
       </c>
       <c r="D24" s="3">
-        <v>2120</v>
+        <v>17576</v>
       </c>
       <c r="E24" s="4">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F24" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G24" s="7">
         <f t="shared" si="1"/>
-        <v>115380</v>
+        <v>0</v>
       </c>
       <c r="H24" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="2"/>
-        <v>135380</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.45">
@@ -1432,31 +1462,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C25" s="3">
-        <v>13493</v>
+        <v>12119</v>
       </c>
       <c r="D25" s="3">
-        <v>13532</v>
+        <v>12119</v>
       </c>
       <c r="E25" s="4">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F25" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G25" s="7">
         <f t="shared" si="1"/>
-        <v>149994</v>
+        <v>0</v>
       </c>
       <c r="H25" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="2"/>
-        <v>169994</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.45">
@@ -1464,31 +1494,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="C26" s="3">
-        <v>15888</v>
+        <v>2565</v>
       </c>
       <c r="D26" s="3">
-        <v>16006</v>
+        <v>2566</v>
       </c>
       <c r="E26" s="4">
         <f t="shared" si="0"/>
-        <v>118</v>
+        <v>1</v>
       </c>
       <c r="F26" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G26" s="7">
         <f t="shared" si="1"/>
-        <v>453828</v>
+        <v>2971</v>
       </c>
       <c r="H26" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="2"/>
-        <v>473828</v>
+        <v>27971</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.45">
@@ -1496,31 +1526,31 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C27" s="3">
-        <v>14740</v>
+        <v>16533</v>
       </c>
       <c r="D27" s="3">
-        <v>14873</v>
+        <v>16577</v>
       </c>
       <c r="E27" s="4">
         <f t="shared" si="0"/>
-        <v>133</v>
+        <v>44</v>
       </c>
       <c r="F27" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G27" s="7">
         <f t="shared" si="1"/>
-        <v>511518</v>
+        <v>130724</v>
       </c>
       <c r="H27" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="2"/>
-        <v>531518</v>
+        <v>155724</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
@@ -1528,31 +1558,31 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="C28" s="3">
-        <v>456</v>
+        <v>1604</v>
       </c>
       <c r="D28" s="3">
-        <v>480</v>
+        <v>1604</v>
       </c>
       <c r="E28" s="4">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F28" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G28" s="7">
         <f t="shared" si="1"/>
-        <v>92304</v>
+        <v>0</v>
       </c>
       <c r="H28" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="2"/>
-        <v>112304</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.45">
@@ -1560,31 +1590,31 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C29" s="3">
-        <v>182</v>
+        <v>18651</v>
       </c>
       <c r="D29" s="3">
-        <v>182</v>
+        <v>18848</v>
       </c>
       <c r="E29" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="F29" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G29" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>585287</v>
       </c>
       <c r="H29" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="2"/>
-        <v>20000</v>
+        <v>610287</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.45">
@@ -1592,31 +1622,31 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C30" s="3">
-        <v>3997</v>
+        <v>14873</v>
       </c>
       <c r="D30" s="3">
-        <v>4062</v>
+        <v>14873</v>
       </c>
       <c r="E30" s="4">
         <f t="shared" si="0"/>
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="F30" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G30" s="7">
         <f t="shared" si="1"/>
-        <v>249990</v>
+        <v>0</v>
       </c>
       <c r="H30" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="2"/>
-        <v>269990</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.45">
@@ -1624,31 +1654,31 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C31" s="3">
-        <v>6336</v>
+        <v>510</v>
       </c>
       <c r="D31" s="3">
-        <v>6773</v>
+        <v>510</v>
       </c>
       <c r="E31" s="4">
         <f t="shared" si="0"/>
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="F31" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G31" s="7">
         <f t="shared" si="1"/>
-        <v>1680702</v>
+        <v>0</v>
       </c>
       <c r="H31" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="2"/>
-        <v>1700702</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.45">
@@ -1656,31 +1686,31 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C32" s="3">
-        <v>13212</v>
+        <v>182</v>
       </c>
       <c r="D32" s="3">
-        <v>13213</v>
+        <v>182</v>
       </c>
       <c r="E32" s="4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G32" s="7">
         <f t="shared" si="1"/>
-        <v>3846</v>
+        <v>0</v>
       </c>
       <c r="H32" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="2"/>
-        <v>23846</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.45">
@@ -1688,31 +1718,31 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C33" s="3">
-        <v>11930</v>
+        <v>5830</v>
       </c>
       <c r="D33" s="3">
-        <v>12533</v>
+        <v>5906</v>
       </c>
       <c r="E33" s="4">
         <f t="shared" si="0"/>
-        <v>603</v>
+        <v>76</v>
       </c>
       <c r="F33" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G33" s="7">
         <f t="shared" si="1"/>
-        <v>2319138</v>
+        <v>225796</v>
       </c>
       <c r="H33" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="2"/>
-        <v>2339138</v>
+        <v>250796</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.45">
@@ -1720,31 +1750,31 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C34" s="3">
-        <v>25642</v>
+        <v>8809</v>
       </c>
       <c r="D34" s="3">
-        <v>25931</v>
+        <v>8907</v>
       </c>
       <c r="E34" s="4">
         <f t="shared" si="0"/>
-        <v>289</v>
+        <v>98</v>
       </c>
       <c r="F34" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G34" s="7">
         <f t="shared" si="1"/>
-        <v>1111494</v>
+        <v>291158</v>
       </c>
       <c r="H34" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="2"/>
-        <v>1131494</v>
+        <v>316158</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.45">
@@ -1752,31 +1782,31 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C35" s="3">
-        <v>1847</v>
+        <v>15489</v>
       </c>
       <c r="D35" s="3">
-        <v>2111</v>
+        <v>15588</v>
       </c>
       <c r="E35" s="4">
         <f t="shared" si="0"/>
-        <v>264</v>
+        <v>99</v>
       </c>
       <c r="F35" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G35" s="7">
         <f t="shared" si="1"/>
-        <v>1015344</v>
+        <v>294129</v>
       </c>
       <c r="H35" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I35" s="5">
         <f t="shared" si="2"/>
-        <v>1035344</v>
+        <v>319129</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.45">
@@ -1784,31 +1814,31 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C36" s="3">
-        <v>12228</v>
+        <v>15589</v>
       </c>
       <c r="D36" s="3">
-        <v>12228</v>
+        <v>15688</v>
       </c>
       <c r="E36" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="F36" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G36" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>294129</v>
       </c>
       <c r="H36" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" si="2"/>
-        <v>20000</v>
+        <v>319129</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.45">
@@ -1816,31 +1846,31 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C37" s="3">
-        <v>2273</v>
+        <v>28758</v>
       </c>
       <c r="D37" s="3">
-        <v>2276</v>
+        <v>28928</v>
       </c>
       <c r="E37" s="4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>170</v>
       </c>
       <c r="F37" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G37" s="7">
         <f t="shared" si="1"/>
-        <v>11538</v>
+        <v>505070</v>
       </c>
       <c r="H37" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="2"/>
-        <v>31538</v>
+        <v>530070</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.45">
@@ -1848,31 +1878,31 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C38" s="3">
-        <v>4997</v>
+        <v>1157</v>
       </c>
       <c r="D38" s="3">
-        <v>5309</v>
+        <v>1205</v>
       </c>
       <c r="E38" s="4">
         <f t="shared" si="0"/>
-        <v>312</v>
+        <v>48</v>
       </c>
       <c r="F38" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G38" s="7">
         <f t="shared" si="1"/>
-        <v>1199952</v>
+        <v>142608</v>
       </c>
       <c r="H38" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="2"/>
-        <v>1219952</v>
+        <v>167608</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.45">
@@ -1880,31 +1910,31 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="C39" s="3">
-        <v>6234</v>
+        <v>952</v>
       </c>
       <c r="D39" s="3">
-        <v>6356</v>
+        <v>965</v>
       </c>
       <c r="E39" s="4">
         <f t="shared" si="0"/>
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="F39" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G39" s="7">
         <f t="shared" si="1"/>
-        <v>469212</v>
+        <v>38623</v>
       </c>
       <c r="H39" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="2"/>
-        <v>489212</v>
+        <v>63623</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.45">
@@ -1912,31 +1942,31 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C40" s="3">
-        <v>3596</v>
+        <v>12228</v>
       </c>
       <c r="D40" s="3">
-        <v>3747</v>
+        <v>12228</v>
       </c>
       <c r="E40" s="4">
         <f t="shared" si="0"/>
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="F40" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G40" s="7">
         <f t="shared" si="1"/>
-        <v>580746</v>
+        <v>0</v>
       </c>
       <c r="H40" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I40" s="5">
         <f t="shared" si="2"/>
-        <v>600746</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.45">
@@ -1944,31 +1974,31 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="C41" s="3">
-        <v>3300</v>
+        <v>3451</v>
       </c>
       <c r="D41" s="3">
-        <v>3369</v>
+        <v>3451</v>
       </c>
       <c r="E41" s="4">
         <f t="shared" si="0"/>
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F41" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G41" s="7">
         <f t="shared" si="1"/>
-        <v>265374</v>
+        <v>0</v>
       </c>
       <c r="H41" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I41" s="5">
         <f t="shared" si="2"/>
-        <v>285374</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.45">
@@ -1976,31 +2006,31 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C42" s="3">
-        <v>197</v>
+        <v>8235</v>
       </c>
       <c r="D42" s="3">
-        <v>197</v>
+        <v>8304</v>
       </c>
       <c r="E42" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="F42" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G42" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>204999</v>
       </c>
       <c r="H42" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="2"/>
-        <v>20000</v>
+        <v>229999</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.45">
@@ -2008,31 +2038,31 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C43" s="3">
-        <v>7569</v>
+        <v>8152</v>
       </c>
       <c r="D43" s="3">
-        <v>7569</v>
+        <v>8246</v>
       </c>
       <c r="E43" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="F43" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G43" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>279274</v>
       </c>
       <c r="H43" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I43" s="5">
         <f t="shared" si="2"/>
-        <v>20000</v>
+        <v>304274</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.45">
@@ -2040,31 +2070,31 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="C44" s="3">
-        <v>0</v>
+        <v>6678</v>
       </c>
       <c r="D44" s="3">
-        <v>502</v>
+        <v>6814</v>
       </c>
       <c r="E44" s="4">
         <f t="shared" si="0"/>
-        <v>502</v>
+        <v>136</v>
       </c>
       <c r="F44" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G44" s="7">
         <f t="shared" si="1"/>
-        <v>1930692</v>
+        <v>404056</v>
       </c>
       <c r="H44" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I44" s="5">
         <f t="shared" si="2"/>
-        <v>1950692</v>
+        <v>429056</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.45">
@@ -2072,31 +2102,31 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="C45" s="3">
-        <v>4416</v>
+        <v>4776</v>
       </c>
       <c r="D45" s="3">
-        <v>4416</v>
+        <v>4876</v>
       </c>
       <c r="E45" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F45" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G45" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>297100</v>
       </c>
       <c r="H45" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I45" s="5">
         <f t="shared" si="2"/>
-        <v>20000</v>
+        <v>322100</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.45">
@@ -2104,31 +2134,31 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C46" s="3">
-        <v>25258</v>
+        <v>224</v>
       </c>
       <c r="D46" s="3">
-        <v>25743</v>
+        <v>224</v>
       </c>
       <c r="E46" s="4">
         <f t="shared" si="0"/>
-        <v>485</v>
+        <v>0</v>
       </c>
       <c r="F46" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G46" s="7">
         <f t="shared" si="1"/>
-        <v>1865310</v>
+        <v>0</v>
       </c>
       <c r="H46" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="2"/>
-        <v>1885310</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.45">
@@ -2136,31 +2166,31 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C47" s="3">
-        <v>8794</v>
+        <v>9039</v>
       </c>
       <c r="D47" s="3">
-        <v>9221</v>
+        <v>9039</v>
       </c>
       <c r="E47" s="4">
         <f t="shared" si="0"/>
-        <v>427</v>
+        <v>0</v>
       </c>
       <c r="F47" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G47" s="7">
         <f t="shared" si="1"/>
-        <v>1642242</v>
+        <v>0</v>
       </c>
       <c r="H47" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I47" s="5">
         <f t="shared" si="2"/>
-        <v>1662242</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.45">
@@ -2168,31 +2198,31 @@
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C48" s="3">
-        <v>8460</v>
+        <v>636</v>
       </c>
       <c r="D48" s="3">
-        <v>8491</v>
+        <v>636</v>
       </c>
       <c r="E48" s="4">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F48" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G48" s="7">
         <f t="shared" si="1"/>
-        <v>119226</v>
+        <v>0</v>
       </c>
       <c r="H48" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I48" s="5">
         <f t="shared" si="2"/>
-        <v>139226</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.45">
@@ -2200,31 +2230,31 @@
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C49" s="3">
-        <v>76985</v>
+        <v>4785</v>
       </c>
       <c r="D49" s="3">
-        <v>81885</v>
+        <v>4785</v>
       </c>
       <c r="E49" s="4">
         <f t="shared" si="0"/>
-        <v>4900</v>
+        <v>0</v>
       </c>
       <c r="F49" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G49" s="7">
         <f t="shared" si="1"/>
-        <v>18845400</v>
+        <v>0</v>
       </c>
       <c r="H49" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I49" s="5">
         <f t="shared" si="2"/>
-        <v>18865400</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.45">
@@ -2232,31 +2262,31 @@
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="C50" s="3">
-        <v>31824</v>
-      </c>
-      <c r="D50" s="3">
-        <v>31881</v>
+        <v>28461</v>
+      </c>
+      <c r="D50" s="9">
+        <v>28474</v>
       </c>
       <c r="E50" s="4">
         <f t="shared" si="0"/>
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="F50" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G50" s="7">
         <f t="shared" si="1"/>
-        <v>219222</v>
+        <v>38623</v>
       </c>
       <c r="H50" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I50" s="5">
         <f t="shared" si="2"/>
-        <v>239222</v>
+        <v>63623</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.45">
@@ -2264,31 +2294,31 @@
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C51" s="3">
-        <v>8342</v>
+        <v>9989</v>
       </c>
       <c r="D51" s="3">
-        <v>8348</v>
+        <v>9989</v>
       </c>
       <c r="E51" s="4">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F51" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G51" s="7">
         <f t="shared" si="1"/>
-        <v>23076</v>
+        <v>0</v>
       </c>
       <c r="H51" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I51" s="5">
         <f t="shared" si="2"/>
-        <v>43076</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.45">
@@ -2296,31 +2326,31 @@
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="C52" s="3">
-        <v>18028</v>
+        <v>339</v>
       </c>
       <c r="D52" s="3">
-        <v>18091</v>
+        <v>339</v>
       </c>
       <c r="E52" s="4">
         <f t="shared" si="0"/>
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="F52" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G52" s="7">
         <f t="shared" si="1"/>
-        <v>242298</v>
+        <v>0</v>
       </c>
       <c r="H52" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I52" s="5">
         <f t="shared" si="2"/>
-        <v>262298</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.45">
@@ -2328,31 +2358,31 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C53" s="3">
-        <v>5997</v>
+        <v>9005</v>
       </c>
       <c r="D53" s="3">
-        <v>6281</v>
+        <v>9005</v>
       </c>
       <c r="E53" s="4">
         <f t="shared" si="0"/>
-        <v>284</v>
+        <v>0</v>
       </c>
       <c r="F53" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G53" s="7">
         <f t="shared" si="1"/>
-        <v>1092264</v>
+        <v>0</v>
       </c>
       <c r="H53" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I53" s="5">
         <f t="shared" si="2"/>
-        <v>1112264</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.45">
@@ -2360,31 +2390,31 @@
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="C54" s="3">
-        <v>10486</v>
+        <v>109097</v>
       </c>
       <c r="D54" s="3">
-        <v>10815</v>
+        <v>109173</v>
       </c>
       <c r="E54" s="4">
         <f t="shared" si="0"/>
-        <v>329</v>
+        <v>76</v>
       </c>
       <c r="F54" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G54" s="7">
         <f t="shared" si="1"/>
-        <v>1265334</v>
+        <v>225796</v>
       </c>
       <c r="H54" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I54" s="5">
         <f t="shared" si="2"/>
-        <v>1285334</v>
+        <v>250796</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.45">
@@ -2392,31 +2422,31 @@
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C55" s="3">
-        <v>8434</v>
+        <v>33610</v>
       </c>
       <c r="D55" s="3">
-        <v>8623</v>
+        <v>33660</v>
       </c>
       <c r="E55" s="4">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>50</v>
       </c>
       <c r="F55" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G55" s="7">
         <f t="shared" si="1"/>
-        <v>726894</v>
+        <v>148550</v>
       </c>
       <c r="H55" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I55" s="5">
         <f t="shared" si="2"/>
-        <v>746894</v>
+        <v>173550</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.45">
@@ -2424,31 +2454,31 @@
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C56" s="3">
-        <v>7221</v>
+        <v>11158</v>
       </c>
       <c r="D56" s="3">
-        <v>7318</v>
+        <v>11158</v>
       </c>
       <c r="E56" s="4">
         <f t="shared" si="0"/>
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="F56" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G56" s="7">
         <f t="shared" si="1"/>
-        <v>373062</v>
+        <v>0</v>
       </c>
       <c r="H56" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I56" s="5">
         <f t="shared" si="2"/>
-        <v>393062</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.45">
@@ -2456,31 +2486,32 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C57" s="3">
-        <v>9317</v>
+        <v>18983</v>
       </c>
       <c r="D57" s="3">
-        <v>9373</v>
+        <f>18953+30+20</f>
+        <v>19003</v>
       </c>
       <c r="E57" s="4">
         <f t="shared" si="0"/>
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="F57" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G57" s="7">
         <f t="shared" si="1"/>
-        <v>215376</v>
+        <v>59420</v>
       </c>
       <c r="H57" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I57" s="5">
         <f t="shared" si="2"/>
-        <v>235376</v>
+        <v>84420</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.45">
@@ -2488,31 +2519,32 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C58" s="3">
-        <v>12841</v>
+        <v>8168</v>
       </c>
       <c r="D58" s="3">
-        <v>13762</v>
+        <f>8168+15</f>
+        <v>8183</v>
       </c>
       <c r="E58" s="4">
         <f t="shared" si="0"/>
-        <v>921</v>
+        <v>15</v>
       </c>
       <c r="F58" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G58" s="7">
         <f t="shared" si="1"/>
-        <v>3542166</v>
+        <v>44565</v>
       </c>
       <c r="H58" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I58" s="5">
         <f t="shared" si="2"/>
-        <v>3562166</v>
+        <v>69565</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.45">
@@ -2520,31 +2552,31 @@
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C59" s="3">
-        <v>27834</v>
+        <v>14891</v>
       </c>
       <c r="D59" s="3">
-        <v>28734</v>
+        <v>15059</v>
       </c>
       <c r="E59" s="4">
         <f t="shared" si="0"/>
-        <v>900</v>
+        <v>168</v>
       </c>
       <c r="F59" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G59" s="7">
         <f t="shared" si="1"/>
-        <v>3461400</v>
+        <v>499128</v>
       </c>
       <c r="H59" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I59" s="5">
         <f t="shared" si="2"/>
-        <v>3481400</v>
+        <v>524128</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.45">
@@ -2552,31 +2584,31 @@
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C60" s="3">
-        <v>56194</v>
+        <v>9986</v>
       </c>
       <c r="D60" s="3">
-        <v>56453</v>
+        <v>9986</v>
       </c>
       <c r="E60" s="4">
         <f t="shared" si="0"/>
-        <v>259</v>
+        <v>0</v>
       </c>
       <c r="F60" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G60" s="7">
         <f t="shared" si="1"/>
-        <v>996114</v>
+        <v>0</v>
       </c>
       <c r="H60" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I60" s="5">
         <f t="shared" si="2"/>
-        <v>1016114</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.45">
@@ -2584,31 +2616,32 @@
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C61" s="3">
-        <v>7391</v>
+        <v>8092</v>
       </c>
       <c r="D61" s="3">
-        <v>7456</v>
+        <f>8092+20</f>
+        <v>8112</v>
       </c>
       <c r="E61" s="4">
         <f t="shared" si="0"/>
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F61" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G61" s="7">
         <f t="shared" si="1"/>
-        <v>249990</v>
+        <v>59420</v>
       </c>
       <c r="H61" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I61" s="5">
         <f t="shared" si="2"/>
-        <v>269990</v>
+        <v>84420</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.45">
@@ -2616,31 +2649,31 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C62" s="3">
-        <v>78368</v>
+        <v>11057</v>
       </c>
       <c r="D62" s="3">
-        <v>78368</v>
+        <v>11058</v>
       </c>
       <c r="E62" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G62" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2971</v>
       </c>
       <c r="H62" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I62" s="5">
         <f t="shared" si="2"/>
-        <v>20000</v>
+        <v>27971</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.45">
@@ -2648,31 +2681,31 @@
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C63" s="3">
-        <v>1618</v>
+        <v>28723</v>
       </c>
       <c r="D63" s="3">
-        <v>1618</v>
+        <v>29130</v>
       </c>
       <c r="E63" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>407</v>
       </c>
       <c r="F63" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G63" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1209197</v>
       </c>
       <c r="H63" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I63" s="5">
         <f t="shared" si="2"/>
-        <v>20000</v>
+        <v>1234197</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.45">
@@ -2680,31 +2713,31 @@
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C64" s="3">
-        <v>0</v>
+        <v>36062</v>
       </c>
       <c r="D64" s="3">
-        <v>0</v>
+        <v>36264</v>
       </c>
       <c r="E64" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="F64" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G64" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>600142</v>
       </c>
       <c r="H64" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I64" s="5">
         <f t="shared" si="2"/>
-        <v>20000</v>
+        <v>625142</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.45">
@@ -2712,31 +2745,31 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C65" s="3">
-        <v>7359</v>
+        <v>1490</v>
       </c>
       <c r="D65" s="3">
-        <v>7495</v>
+        <v>1630</v>
       </c>
       <c r="E65" s="4">
         <f t="shared" si="0"/>
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F65" s="6">
-        <v>3846</v>
+        <v>2971</v>
       </c>
       <c r="G65" s="7">
         <f t="shared" si="1"/>
-        <v>523056</v>
+        <v>415940</v>
       </c>
       <c r="H65" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="I65" s="5">
         <f t="shared" si="2"/>
-        <v>543056</v>
+        <v>440940</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.45">
@@ -2744,32 +2777,194 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C66" s="3">
+        <v>9480</v>
+      </c>
+      <c r="D66" s="3">
+        <v>9480</v>
+      </c>
+      <c r="E66" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F66" s="6">
+        <v>2971</v>
+      </c>
+      <c r="G66" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H66" s="4">
+        <v>25000</v>
+      </c>
+      <c r="I66" s="5">
+        <f t="shared" si="2"/>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A67" s="4">
+        <v>66</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3"/>
+      <c r="E67" s="4">
+        <f t="shared" ref="E67:E71" si="3">D67-C67</f>
+        <v>0</v>
+      </c>
+      <c r="F67" s="6">
+        <v>2971</v>
+      </c>
+      <c r="G67" s="7">
+        <f t="shared" ref="G67:G71" si="4">E67*F67</f>
+        <v>0</v>
+      </c>
+      <c r="H67" s="4">
+        <v>25000</v>
+      </c>
+      <c r="I67" s="5">
+        <f t="shared" ref="I67:I71" si="5">G67+H67</f>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A68" s="4">
         <v>67</v>
       </c>
-      <c r="C66" s="3">
-        <v>13205</v>
-      </c>
-      <c r="D66" s="3">
-        <v>13846</v>
-      </c>
-      <c r="E66" s="4">
-        <f t="shared" si="0"/>
-        <v>641</v>
-      </c>
-      <c r="F66" s="6">
-        <v>3846</v>
-      </c>
-      <c r="G66" s="7">
-        <f t="shared" si="1"/>
-        <v>2465286</v>
-      </c>
-      <c r="H66" s="4">
-        <v>20000</v>
-      </c>
-      <c r="I66" s="5">
-        <f t="shared" si="2"/>
-        <v>2485286</v>
-      </c>
+      <c r="B68" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C68">
+        <v>1648</v>
+      </c>
+      <c r="D68" s="3">
+        <v>1648</v>
+      </c>
+      <c r="E68" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F68" s="6">
+        <v>2971</v>
+      </c>
+      <c r="G68" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H68" s="4">
+        <v>25000</v>
+      </c>
+      <c r="I68" s="5">
+        <f t="shared" si="5"/>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A69" s="4">
+        <v>68</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C69">
+        <v>8574</v>
+      </c>
+      <c r="D69" s="3">
+        <v>8574</v>
+      </c>
+      <c r="E69" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F69" s="6">
+        <v>2971</v>
+      </c>
+      <c r="G69" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H69" s="4">
+        <v>25000</v>
+      </c>
+      <c r="I69" s="5">
+        <f t="shared" si="5"/>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A70" s="4">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C70">
+        <v>20612</v>
+      </c>
+      <c r="D70" s="3">
+        <v>20854</v>
+      </c>
+      <c r="E70" s="4">
+        <f t="shared" si="3"/>
+        <v>242</v>
+      </c>
+      <c r="F70" s="6">
+        <v>2971</v>
+      </c>
+      <c r="G70" s="7">
+        <f t="shared" si="4"/>
+        <v>718982</v>
+      </c>
+      <c r="H70" s="4">
+        <v>25000</v>
+      </c>
+      <c r="I70" s="5">
+        <f t="shared" si="5"/>
+        <v>743982</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A71" s="4">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>66</v>
+      </c>
+      <c r="C71" s="10">
+        <v>3595</v>
+      </c>
+      <c r="D71" s="3">
+        <v>3595</v>
+      </c>
+      <c r="E71" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F71" s="6">
+        <v>2971</v>
+      </c>
+      <c r="G71" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H71" s="4">
+        <v>25000</v>
+      </c>
+      <c r="I71" s="5">
+        <f t="shared" si="5"/>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="G72" s="11"/>
+      <c r="I72" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
